--- a/artfynd/A 11656-2025 artfynd.xlsx
+++ b/artfynd/A 11656-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102772811</v>
+        <v>102772828</v>
       </c>
       <c r="B6" t="n">
-        <v>73507</v>
+        <v>73678</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449735.1919738768</v>
+        <v>449460.1609073878</v>
       </c>
       <c r="R6" t="n">
-        <v>6546190.141389573</v>
+        <v>6546204.048165654</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1241,6 +1241,575 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102772827</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83352</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1971</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stor sotdyna</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Camarops polysperma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Mont.) J.H.Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövöbotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>449385.6317065295</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546141.237675542</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Visnum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-11-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-11-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102772821</v>
+      </c>
+      <c r="B8" t="n">
+        <v>73678</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lövöbotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>449348.0541427687</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546105.720873215</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Visnum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-11-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-11-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102772807</v>
+      </c>
+      <c r="B9" t="n">
+        <v>77882</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövöbotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>449375.0719860939</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6546044.140458032</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Visnum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102772811</v>
+      </c>
+      <c r="B10" t="n">
+        <v>73507</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lövöbotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>449735.1919738768</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6546190.141389573</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Visnum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102772805</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57575</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövöbotten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>449361.4427303681</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6546026.827950117</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Visnum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11656-2025 artfynd.xlsx
+++ b/artfynd/A 11656-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102772795</v>
+        <v>102772822</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449748.8459313858</v>
+        <v>449377</v>
       </c>
       <c r="R2" t="n">
-        <v>6546209.511948556</v>
+        <v>6546102</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102772822</v>
+        <v>102772827</v>
       </c>
       <c r="B3" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>1971</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Mont.) J.H.Mill.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449377.3857747136</v>
+        <v>449386</v>
       </c>
       <c r="R3" t="n">
-        <v>6546102.246418759</v>
+        <v>6546141</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2019-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102772792</v>
+        <v>102772811</v>
       </c>
       <c r="B4" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövöbotten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449521.8943148988</v>
+        <v>449735</v>
       </c>
       <c r="R4" t="n">
-        <v>6546195.517492314</v>
+        <v>6546190</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,19 +937,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102772814</v>
+        <v>102772807</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6431</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449476.2297774051</v>
+        <v>449375</v>
       </c>
       <c r="R5" t="n">
-        <v>6546171.939328508</v>
+        <v>6546044</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,19 +1034,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102772828</v>
+        <v>102772821</v>
       </c>
       <c r="B6" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449460.1609073878</v>
+        <v>449348</v>
       </c>
       <c r="R6" t="n">
-        <v>6546204.048165654</v>
+        <v>6546105</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,19 +1131,9 @@
           <t>2019-11-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102772827</v>
+        <v>102772828</v>
       </c>
       <c r="B7" t="n">
-        <v>83352</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1971</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449385.6317065295</v>
+        <v>449460</v>
       </c>
       <c r="R7" t="n">
-        <v>6546141.237675542</v>
+        <v>6546204</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1317,19 +1228,9 @@
           <t>2019-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102772821</v>
+        <v>102772792</v>
       </c>
       <c r="B8" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,34 +1268,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>208250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövöbotten, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449348.0541427687</v>
+        <v>449522</v>
       </c>
       <c r="R8" t="n">
-        <v>6546105.720873215</v>
+        <v>6546196</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,22 +1331,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,15 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102772807</v>
+        <v>102772805</v>
       </c>
       <c r="B9" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,34 +1374,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6431</v>
+        <v>208250</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövöbotten, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449375.0719860939</v>
+        <v>449361</v>
       </c>
       <c r="R9" t="n">
-        <v>6546044.140458032</v>
+        <v>6546027</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,19 +1440,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,15 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102772811</v>
+        <v>102772795</v>
       </c>
       <c r="B10" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449735.1919738768</v>
+        <v>449749</v>
       </c>
       <c r="R10" t="n">
-        <v>6546190.141389573</v>
+        <v>6546209</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1537,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102772805</v>
+        <v>102772814</v>
       </c>
       <c r="B11" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,43 +1577,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208250</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lövöbotten, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449361.4427303681</v>
+        <v>449476</v>
       </c>
       <c r="R11" t="n">
-        <v>6546026.827950117</v>
+        <v>6546172</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1774,19 +1634,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 11656-2025 artfynd.xlsx
+++ b/artfynd/A 11656-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772822</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772827</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772811</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772807</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772821</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772828</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772792</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772795</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,8 +1710,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102772814</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>